--- a/docs/design/蛋仔--大富翁--机会表.xlsx
+++ b/docs/design/蛋仔--大富翁--机会表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lzx_8\Desktop\dev\monopoly\.agents\docs\design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\策划案\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BE9BBE-F71F-418F-95E2-A0954EC10351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00232C9-2B37-4147-ADFC-4B4FD99CD8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -319,17 +319,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -393,12 +393,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -679,15 +680,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.875" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -710,7 +711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,11 +734,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>3001</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="3">
@@ -756,11 +757,11 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3002</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="3">
@@ -779,11 +780,11 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3003</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3">
@@ -802,11 +803,11 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3004</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="3">
@@ -825,11 +826,11 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3005</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="3">
@@ -848,11 +849,11 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>3006</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="3">
@@ -871,11 +872,11 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>3007</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="3">
@@ -894,11 +895,11 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>3008</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="3">
@@ -917,11 +918,11 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>3009</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="3">
@@ -940,11 +941,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>3010</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="3">
@@ -963,11 +964,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>3011</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="3">
@@ -986,11 +987,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>3012</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="3">
@@ -1009,11 +1010,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>3013</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="3">
@@ -1031,13 +1032,34 @@
       <c r="G15" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="J15" s="1">
+        <v>3014</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="3">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>3014</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>3017</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C16" s="3">
         <v>200</v>
@@ -1046,21 +1068,42 @@
         <v>0</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3015</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="3">
+        <v>200</v>
+      </c>
+      <c r="M16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="3">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="P16" s="3">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>3015</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>3018</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C17" s="3">
         <v>200</v>
@@ -1069,24 +1112,45 @@
         <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3016</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G17" s="3">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="P17" s="3">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>3016</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>3019</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C18" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D18" s="3" t="b">
         <v>0</v>
@@ -1095,64 +1159,130 @@
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3035</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="3">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="P18" s="3">
+        <v>4004</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>3017</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>3020</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C19" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1">
+        <v>3036</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="3">
+        <v>100</v>
+      </c>
+      <c r="M19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="3">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>3018</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>3021</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C20" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="G20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>3037</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>3019</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>3022</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C21" s="3">
         <v>300</v>
@@ -1164,18 +1294,18 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>3020</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>3023</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C22" s="3">
         <v>300</v>
@@ -1187,18 +1317,18 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>3021</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>3024</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C23" s="3">
         <v>300</v>
@@ -1210,21 +1340,21 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>3022</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>3025</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="C24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D24" s="3" t="b">
         <v>0</v>
@@ -1233,21 +1363,21 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>3023</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>3026</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C25" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D25" s="3" t="b">
         <v>0</v>
@@ -1256,21 +1386,21 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G25" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>3024</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>3027</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C26" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D26" s="3" t="b">
         <v>0</v>
@@ -1279,87 +1409,87 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G26" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>3025</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>3028</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C27" s="3">
         <v>200</v>
       </c>
       <c r="D27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" s="3">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>3026</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>3029</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C28" s="3">
         <v>200</v>
       </c>
       <c r="D28" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="3">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>3027</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>3030</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C29" s="3">
         <v>200</v>
       </c>
       <c r="D29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G29" s="3">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>3028</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>3031</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C30" s="3">
         <v>200</v>
@@ -1371,18 +1501,18 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>44</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>3029</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>37</v>
+        <v>3032</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C31" s="3">
         <v>200</v>
@@ -1394,18 +1524,18 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>44</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>3030</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>3033</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="3">
         <v>200</v>
@@ -1417,24 +1547,24 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>44</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>3031</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>43</v>
+        <v>3034</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="C33" s="3">
         <v>200</v>
       </c>
       <c r="D33" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>12</v>
@@ -1443,148 +1573,7 @@
         <v>44</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1">
-        <v>3032</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="3">
-        <v>200</v>
-      </c>
-      <c r="D34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="1">
-        <v>3033</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="3">
-        <v>200</v>
-      </c>
-      <c r="D35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="1">
-        <v>3034</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="3">
-        <v>200</v>
-      </c>
-      <c r="D36" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G36" s="3" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="1">
-        <v>3035</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="3">
-        <v>100</v>
-      </c>
-      <c r="D37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G37" s="3">
-        <v>4004</v>
-      </c>
-      <c r="H37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1">
-        <v>3036</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="3">
-        <v>100</v>
-      </c>
-      <c r="D38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G38" s="3">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1">
-        <v>3037</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="3">
-        <v>100</v>
-      </c>
-      <c r="D39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="3">
-        <v>4006</v>
       </c>
     </row>
   </sheetData>
